--- a/stories/arbres/ATOM-SAN.SOM.001-08.xlsx
+++ b/stories/arbres/ATOM-SAN.SOM.001-08.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le soir arrive. La lampe de la chambre est douce. Bertrand bâille. Ses yeux piquent un peu. Papa dit : le corps a besoin de dormir. Ce n'est pas une punition. C'est le dodo. Papa tend le pyjama. Le tissu est chaud. Bertrand met le pyjama. Il boutonne. Il glisse sous la couverture. Le lit est moelleux. Papa ouvre un livre. Il raconte une histoire courte. Bertrand écoute. Parce que le pyjama est mis, le corps se calme. Papa dit : soir, pyjama, dodo. Bertrand pose sa tête. Il ferme les yeux. Papa reste un moment. Le dodo commence.</t>
+          <t>Le soir arrive. La lampe de la chambre est douce. Bertrand bâille. Ses yeux piquent un peu. Le corps a besoin de dormir. Ce n'est pas une punition. C'est le dodo. Papa tend le pyjama. Le tissu est chaud. Bertrand met le pyjama. Il boutonne. Il glisse sous la couverture. Le lit est moelleux. Papa ouvre un livre. Il raconte une histoire courte. Bertrand écoute. Parce que le pyjama est mis, le corps se calme. Soir, pyjama, dodo. Bertrand pose sa tête. Il ferme les yeux. Papa reste un moment. Le dodo commence.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir arrive. La lampe de la chambre est douce. Bertrand bâille. Ses yeux piquent un peu.
+papa|Le corps a besoin de dormir. Ce n'est pas une punition. C'est le dodo. Papa tend le pyjama.
+narrateur|Le tissu est chaud. Bertrand met le pyjama. Il boutonne. Il glisse sous la couverture. Le lit est moelleux. Papa ouvre un livre. Il raconte une histoire courte. Bertrand écoute. Parce que le pyjama est mis, le corps se calme.
+papa|Soir, pyjama, dodo.
+narrateur|Bertrand pose sa tête. Il ferme les yeux. Papa reste un moment. Le dodo commence.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1494,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, Bertrand va au lit. Que met-il ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1667,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Bertrand a mis le pyjama. Il s'est couché. Le soir, c'est le dodo.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1799,6 +1834,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Papa baisse la lampe. Bertrand respire.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1961,6 +2001,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1979,7 +2024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1996,6 +2041,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.SOM.001-08.xlsx
+++ b/stories/arbres/ATOM-SAN.SOM.001-08.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,11 @@
 narrateur|Bertrand pose sa tête. Il ferme les yeux. Papa reste un moment. Le dodo commence.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1501,6 +1511,7 @@
           <t>narrateur|Le soir, Bertrand va au lit. Que met-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1672,6 +1683,7 @@
           <t>narrateur|Bertrand a mis le pyjama. Il s'est couché. Le soir, c'est le dodo.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1839,6 +1851,7 @@
           <t>narrateur|Papa baisse la lampe. Bertrand respire.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2006,6 +2019,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2024,7 +2038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2048,6 +2062,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2062,7 +2090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2249,6 +2277,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SAN.SOM.001-08.xlsx
+++ b/stories/arbres/ATOM-SAN.SOM.001-08.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bertrand met son pyjama</t>
+          <t>Le bouton du pyjama</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Un bouton brille sur le pyjama plié. Un hibou de tissu écoute. Victorino boutonne. Papa lit. Victorino se couche. Soir, pyjama, dodo.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le soir arrive. La lampe de la chambre est douce. Bertrand bâille. Ses yeux piquent un peu. Le corps a besoin de dormir. Ce n'est pas une punition. C'est le dodo. Papa tend le pyjama. Le tissu est chaud. Bertrand met le pyjama. Il boutonne. Il glisse sous la couverture. Le lit est moelleux. Papa ouvre un livre. Il raconte une histoire courte. Bertrand écoute. Parce que le pyjama est mis, le corps se calme. Soir, pyjama, dodo. Bertrand pose sa tête. Il ferme les yeux. Papa reste un moment. Le dodo commence.</t>
+          <t>Un bouton rond brille sur le pyjama plié. Le pyjama est posé comme un petit tas. Sur le rideau, un hibou de tissu écoute. La lampe fait un cercle chaud au sol. Une chaussette dépasse du tiroir. Dehors, une branche frotte le volet. Ça fait chhh, tout doux. Victorino vit ici, avec papa et maman. Maman est à la cuisine, tout près. En ce moment, Victorino bâille. Ses yeux piquent un peu. Tu bâilles, Victorino ? Oui, papa. Les yeux piquent. Le corps a besoin de dormir. Ce n'est pas une punition. C'est le dodo. Voici le pyjama. Papa tend le pyjama. Le tissu est chaud. Le bouton brille. Oui. Tu boutonnnes, tout doux. Victorino met le pyjama. Il boutonne. Le bouton rentre dans sa maison ronde. Bravo. Tu as mis le pyjama. Le soir, pyjama, dodo. Victorino glisse sous la couverture. Le lit est moelleux. Le hibou écoute, papa. Oui. Il écoute l'histoire. Papa ouvre un livre. Il raconte une histoire courte. Un hibou marche sur une branche. Victorino écoute. Parce que le pyjama est mis, le corps se calme. Soir, pyjama, dodo. Je pose ma tête ? Oui. Tu poses ta tête. Victorino pose sa tête. Il ferme les yeux. Je reste un moment. Bravo, Victorino. Tu as fait du bon travail. Le dodo commence. Le cercle de la lampe rétrécit. La branche fait encore chhh.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,18 +1324,55 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Le soir arrive. La lampe de la chambre est douce. Bertrand bâille. Ses yeux piquent un peu.
-papa|Le corps a besoin de dormir. Ce n'est pas une punition. C'est le dodo. Papa tend le pyjama.
-narrateur|Le tissu est chaud. Bertrand met le pyjama. Il boutonne. Il glisse sous la couverture. Le lit est moelleux. Papa ouvre un livre. Il raconte une histoire courte. Bertrand écoute. Parce que le pyjama est mis, le corps se calme.
+          <t>narrateur|Un bouton rond brille sur le pyjama plié.
+narrateur|Le pyjama est posé comme un petit tas.
+narrateur|Sur le rideau, un hibou de tissu écoute.
+narrateur|La lampe fait un cercle chaud au sol.
+narrateur|Une chaussette dépasse du tiroir.
+narrateur|Dehors, une branche frotte le volet.
+narrateur|Ça fait chhh, tout doux.
+narrateur|Victorino vit ici, avec papa et maman.
+narrateur|Maman est à la cuisine, tout près.
+narrateur|En ce moment, Victorino bâille.
+narrateur|Ses yeux piquent un peu.
+papa|Tu bâilles, Victorino ?
+enfant-m|Oui, papa. Les yeux piquent.
+papa|Le corps a besoin de dormir.
+papa|Ce n'est pas une punition.
+papa|C'est le dodo.
+papa|Voici le pyjama.
+narrateur|Papa tend le pyjama.
+narrateur|Le tissu est chaud.
+enfant-m|Le bouton brille.
+papa|Oui. Tu boutonnnes, tout doux.
+narrateur|Victorino met le pyjama.
+narrateur|Il boutonne.
+narrateur|Le bouton rentre dans sa maison ronde.
+papa|Bravo. Tu as mis le pyjama.
+papa|Le soir, pyjama, dodo.
+narrateur|Victorino glisse sous la couverture.
+narrateur|Le lit est moelleux.
+enfant-m|Le hibou écoute, papa.
+papa|Oui. Il écoute l'histoire.
+narrateur|Papa ouvre un livre.
+narrateur|Il raconte une histoire courte.
+narrateur|Un hibou marche sur une branche.
+narrateur|Victorino écoute.
+narrateur|Parce que le pyjama est mis, le corps se calme.
 papa|Soir, pyjama, dodo.
-narrateur|Bertrand pose sa tête. Il ferme les yeux. Papa reste un moment. Le dodo commence.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>enfants_parc</t>
-        </is>
-      </c>
+enfant-m|Je pose ma tête ?
+papa|Oui. Tu poses ta tête.
+narrateur|Victorino pose sa tête.
+narrateur|Il ferme les yeux.
+papa|Je reste un moment.
+papa|Bravo, Victorino.
+papa|Tu as fait du bon travail.
+narrateur|Le dodo commence.
+narrateur|Le cercle de la lampe rétrécit.
+narrateur|La branche fait encore chhh.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1348,7 +1397,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Bertrand va au lit. Que met-il ?</t>
+          <t>Le soir, Victorino va au lit. Que met-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1508,7 +1557,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Le soir, Bertrand va au lit. Que met-il ?</t>
+          <t>narrateur|Le soir, Victorino va au lit.
+narrateur|Que met-il ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1536,7 +1586,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Bertrand a mis le pyjama. Il s'est couché. Le soir, c'est le dodo.</t>
+          <t>Victorino a mis le pyjama. Il s'est couché. Tu as boutonné le pyjama ? Oui, papa. Bravo. Le soir, c'est le dodo. Le hibou de tissu écoute encore.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1680,7 +1730,12 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Bertrand a mis le pyjama. Il s'est couché. Le soir, c'est le dodo.</t>
+          <t>narrateur|Victorino a mis le pyjama.
+narrateur|Il s'est couché.
+papa|Tu as boutonné le pyjama ?
+enfant-m|Oui, papa.
+papa|Bravo. Le soir, c'est le dodo.
+narrateur|Le hibou de tissu écoute encore.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1708,7 +1763,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Papa baisse la lampe. Bertrand respire.</t>
+          <t>Je baisse la lampe. Le cercle est tout petit. Oui. Tout petit. Victorino respire. Le pyjama est chaud. Tu es bien au lit ? Oui. La branche se tait un moment.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1848,7 +1903,14 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Papa baisse la lampe. Bertrand respire.</t>
+          <t>papa|Je baisse la lampe.
+enfant-m|Le cercle est tout petit.
+papa|Oui. Tout petit.
+narrateur|Victorino respire.
+narrateur|Le pyjama est chaud.
+papa|Tu es bien au lit ?
+enfant-m|Oui.
+narrateur|La branche se tait un moment.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1876,7 +1938,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai mis le pyjama. Le dodo a commencé. Bravo, Victorino. Tu as fait du bon travail. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2016,7 +2078,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai mis le pyjama.
+enfant-m|Le dodo a commencé.
+papa|Bravo, Victorino.
+papa|Tu as fait du bon travail.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2038,7 +2104,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2076,6 +2142,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.SOM.001-08.xlsx
+++ b/stories/arbres/ATOM-SAN.SOM.001-08.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Un bouton rond brille sur le pyjama plié. Le pyjama est posé comme un petit tas. Sur le rideau, un hibou de tissu écoute. La lampe fait un cercle chaud au sol. Une chaussette dépasse du tiroir. Dehors, une branche frotte le volet. Ça fait chhh, tout doux. Victorino vit ici, avec papa et maman. Maman est à la cuisine, tout près. En ce moment, Victorino bâille. Ses yeux piquent un peu. Tu bâilles, Victorino ? Oui, papa. Les yeux piquent. Le corps a besoin de dormir. Ce n'est pas une punition. C'est le dodo. Voici le pyjama. Papa tend le pyjama. Le tissu est chaud. Le bouton brille. Oui. Tu boutonnnes, tout doux. Victorino met le pyjama. Il boutonne. Le bouton rentre dans sa maison ronde. Bravo. Tu as mis le pyjama. Le soir, pyjama, dodo. Victorino glisse sous la couverture. Le lit est moelleux. Le hibou écoute, papa. Oui. Il écoute l'histoire. Papa ouvre un livre. Il raconte une histoire courte. Un hibou marche sur une branche. Victorino écoute. Parce que le pyjama est mis, le corps se calme. Soir, pyjama, dodo. Je pose ma tête ? Oui. Tu poses ta tête. Victorino pose sa tête. Il ferme les yeux. Je reste un moment. Bravo, Victorino. Tu as fait du bon travail. Le dodo commence. Le cercle de la lampe rétrécit. La branche fait encore chhh.</t>
+          <t>Un bouton rond brille sur le pyjama plié. Le pyjama est posé comme un petit tas. Le tas a des plis, tout mous. Sur le rideau, un hibou de tissu écoute. Un œil du hibou est un peu de travers. La lampe fait un cercle chaud au sol. Une chaussette dépasse du tiroir. Dehors, une branche frotte le volet. Ça fait chhh, tout doux. Victorino vit ici, avec papa. Une tasse refroidit sur le rebord. En ce moment, Victorino bâille. Ses yeux piquent un peu. Tu bâilles, Victorino ? Oui, papa. Les yeux piquent. Le corps a besoin de dormir. Ce n'est pas une punition. C'est le dodo. Voici ton pyjama. Papa tend le pyjama. Le tissu est chaud. Le bouton brille. Oui. Tu boutonnes, tout doux. Victorino met le pyjama. Il boutonne. Le bouton rentre dans sa maison ronde. Il est rentré, papa. Oui. Bravo. Tu as mis le pyjama. Le soir, pyjama, dodo. Victorino glisse sous la couverture. Le lit est moelleux. Le hibou écoute, papa. Oui. Il écoute l'histoire. Papa ouvre un livre. Les pages sentent le papier. Il raconte une histoire courte. Un hibou marche sur une branche. La branche est douce, comme le rideau. Il écoute, lui aussi ? Oui. Comme le nôtre. Victorino écoute. Parce que le pyjama est mis, le corps se calme. Soir, pyjama, dodo. Je pose ma tête ? Oui. Tu poses ta tête. Victorino pose sa tête. Il ferme les yeux. Je reste un moment. Bravo, Victorino. Le dodo commence. Le cercle de la lampe rétrécit. La branche fait encore chhh.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le &lt;emphasis level="moderate"&gt;soir&lt;/emphasis&gt; arrive. La lampe de la chambre est douce. Bertrand bâille. Ses yeux piquent un peu. Papa dit : le corps a besoin de dormir. Ce n'est pas une punition. C'est le dodo. Papa tend le pyjama. Le tissu est chaud. Bertrand met le pyjama. Il boutonne. Il glisse sous la couverture. Le lit est moelleux. Papa ouvre un livre. Il raconte une histoire courte. Bertrand écoute. Parce que le pyjama est mis, le corps se calme. Papa dit : soir, pyjama, dodo. Bertrand pose sa tête. Il ferme les yeux. Papa reste un moment. Le dodo commence.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un bouton rond brille sur le pyjama plié. Le pyjama est posé comme un petit tas. Le tas a des plis, tout mous. Sur le rideau, un hibou de tissu écoute. Un œil du hibou est un peu de travers. La lampe fait un cercle chaud au sol. Une chaussette dépasse du tiroir. Dehors, une branche frotte le volet. Ça fait chhh, tout doux. Victorino vit ici, avec papa. Une tasse refroidit sur le rebord. En ce moment, Victorino bâille. Ses yeux piquent un peu. Tu bâilles, Victorino ? Oui, papa. Les yeux piquent. Le corps a besoin de dormir. Ce n'est pas une punition. C'est le dodo. Voici ton pyjama. Papa tend le pyjama. Le tissu est chaud. Le bouton brille. Oui. Tu boutonnes, tout doux. Victorino met le pyjama. Il boutonne. Le bouton rentre dans sa maison ronde. Il est rentré, papa. Oui. Bravo. Tu as mis le pyjama. Le soir, pyjama, dodo. Victorino glisse sous la couverture. Le lit est moelleux. Le hibou écoute, papa. Oui. Il écoute l'histoire. Papa ouvre un livre. Les pages sentent le papier. Il raconte une histoire courte. Un hibou marche sur une branche. La branche est douce, comme le rideau. Il écoute, lui aussi ? Oui. Comme le nôtre. Victorino écoute. Parce que le pyjama est mis, le corps se calme. Soir, pyjama, dodo. Je pose ma tête ? Oui. Tu poses ta tête. Victorino pose sa tête. Il ferme les yeux. Je reste un moment. Bravo, Victorino. Le dodo commence. Le cercle de la lampe rétrécit. La branche fait encore chhh.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1326,13 +1326,15 @@
         <is>
           <t>narrateur|Un bouton rond brille sur le pyjama plié.
 narrateur|Le pyjama est posé comme un petit tas.
+narrateur|Le tas a des plis, tout mous.
 narrateur|Sur le rideau, un hibou de tissu écoute.
+narrateur|Un œil du hibou est un peu de travers.
 narrateur|La lampe fait un cercle chaud au sol.
 narrateur|Une chaussette dépasse du tiroir.
 narrateur|Dehors, une branche frotte le volet.
 narrateur|Ça fait chhh, tout doux.
-narrateur|Victorino vit ici, avec papa et maman.
-narrateur|Maman est à la cuisine, tout près.
+narrateur|Victorino vit ici, avec papa.
+narrateur|Une tasse refroidit sur le rebord.
 narrateur|En ce moment, Victorino bâille.
 narrateur|Ses yeux piquent un peu.
 papa|Tu bâilles, Victorino ?
@@ -1340,23 +1342,29 @@
 papa|Le corps a besoin de dormir.
 papa|Ce n'est pas une punition.
 papa|C'est le dodo.
-papa|Voici le pyjama.
+papa|Voici ton pyjama.
 narrateur|Papa tend le pyjama.
 narrateur|Le tissu est chaud.
 enfant-m|Le bouton brille.
-papa|Oui. Tu boutonnnes, tout doux.
+papa|Oui. Tu boutonnes, tout doux.
 narrateur|Victorino met le pyjama.
 narrateur|Il boutonne.
 narrateur|Le bouton rentre dans sa maison ronde.
-papa|Bravo. Tu as mis le pyjama.
+enfant-m|Il est rentré, papa.
+papa|Oui. Bravo.
+papa|Tu as mis le pyjama.
 papa|Le soir, pyjama, dodo.
 narrateur|Victorino glisse sous la couverture.
 narrateur|Le lit est moelleux.
 enfant-m|Le hibou écoute, papa.
 papa|Oui. Il écoute l'histoire.
 narrateur|Papa ouvre un livre.
+narrateur|Les pages sentent le papier.
 narrateur|Il raconte une histoire courte.
 narrateur|Un hibou marche sur une branche.
+narrateur|La branche est douce, comme le rideau.
+enfant-m|Il écoute, lui aussi ?
+papa|Oui. Comme le nôtre.
 narrateur|Victorino écoute.
 narrateur|Parce que le pyjama est mis, le corps se calme.
 papa|Soir, pyjama, dodo.
@@ -1366,13 +1374,11 @@
 narrateur|Il ferme les yeux.
 papa|Je reste un moment.
 papa|Bravo, Victorino.
-papa|Tu as fait du bon travail.
 narrateur|Le dodo commence.
 narrateur|Le cercle de la lampe rétrécit.
 narrateur|La branche fait encore chhh.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1402,7 +1408,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Le &lt;emphasis level="moderate"&gt;soir&lt;/emphasis&gt;, Bertrand va au lit. Que met-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le soir, Victorino va au lit. Que met-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1561,7 +1567,6 @@
 narrateur|Que met-il ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1591,7 +1596,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Bertrand a mis le pyjama. Il s'est couché. Le &lt;emphasis level="moderate"&gt;soir&lt;/emphasis&gt;, c'est le dodo.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorino a mis le pyjama. Il s'est couché. Tu as boutonné le pyjama ? Oui, papa. Bravo. Le soir, c'est le dodo. Le hibou de tissu écoute encore.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1738,7 +1743,6 @@
 narrateur|Le hibou de tissu écoute encore.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1768,7 +1772,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Papa bais&lt;emphasis level="moderate"&gt;se&lt;/emphasis&gt; la lampe. Bertrand respire.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Je baisse la lampe. Le cercle est tout petit. Oui. Tout petit. Victorino respire. Le pyjama est chaud. Tu es bien au lit ? Oui. La branche se tait un moment.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1913,7 +1917,6 @@
 narrateur|La branche se tait un moment.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1938,12 +1941,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai mis le pyjama. Le dodo a commencé. Bravo, Victorino. Tu as fait du bon travail. L'histoire est finie.</t>
+          <t>J'ai mis le pyjama. Le dodo a commencé. Bravo, Victorino.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai mis le pyjama. Le dodo a commencé. Bravo, Victorino.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2080,12 +2083,9 @@
         <is>
           <t>enfant-m|J'ai mis le pyjama.
 enfant-m|Le dodo a commencé.
-papa|Bravo, Victorino.
-papa|Tu as fait du bon travail.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+papa|Bravo, Victorino.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2104,7 +2104,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2149,6 +2149,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.SOM.001-08.xlsx
+++ b/stories/arbres/ATOM-SAN.SOM.001-08.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bertrand, papa</t>
+          <t>Victorino, papa</t>
         </is>
       </c>
     </row>
